--- a/results/run_1/metrics_pysr.xlsx
+++ b/results/run_1/metrics_pysr.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>Test Time (s)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
@@ -502,39 +507,42 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0009072709912407451</v>
+        <v>0.001822442056239015</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0301209394149775</v>
+        <v>0.04269006976146812</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01262911213950579</v>
+        <v>0.01841747201148197</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2320559151564154</v>
+        <v>0.4377121639128774</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0001800999409642043</v>
+        <v>0.0003876900003596321</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9982501115139931</v>
+        <v>0.9960812006324775</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1322374838452074</v>
+        <v>0.1880176457251871</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0009072385552520099</v>
+        <v>0.001822291752702637</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03012040098093002</v>
+        <v>0.04268830932120218</v>
       </c>
       <c r="K2" t="n">
-        <v>7.139420893835605e-05</v>
+        <v>3.357124756939468e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>103.5603257999992</v>
-      </c>
-      <c r="M2" t="inlineStr">
+        <v>96.75228590000188</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.008501899999828311</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>PySR pour l'année airport</t>
         </is>
